--- a/設計計画エクセル/出席番号氏名.xlsx
+++ b/設計計画エクセル/出席番号氏名.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="H5" s="11">
         <f>_xlfn.F.TEST(C3:C12,F3:F12)</f>
-        <v/>
+        <v>0.956448276969786</v>
       </c>
     </row>
     <row r="6" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -864,9 +864,9 @@
       <c r="F6" s="26" t="n">
         <v>4.33</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="11" t="str">
         <f>IF(H5&gt;0.05,"等分散","不等分散")</f>
-        <v/>
+        <v>等分散</v>
       </c>
     </row>
     <row r="7" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -903,7 +903,7 @@
       </c>
       <c r="H8" s="11">
         <f>_xlfn.T.TEST(C3:C12,F3:F12,2,2)</f>
-        <v/>
+        <v>0.111658451883187</v>
       </c>
     </row>
     <row r="9">
@@ -919,9 +919,9 @@
       <c r="F9" s="26" t="n">
         <v>6.95</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="11" t="str">
         <f>IF(H8&lt;=0.05,"差がある","差があるとは言い切れない")</f>
-        <v/>
+        <v>差があるとは言い切れない</v>
       </c>
     </row>
     <row r="10" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -975,7 +975,7 @@
       </c>
       <c r="C14" s="28">
         <f>AVERAGE(C3:C12)</f>
-        <v/>
+        <v>5.442</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="F14" s="28">
         <f>AVERAGE(F3:F12)</f>
-        <v/>
+        <v>4.579</v>
       </c>
     </row>
     <row r="15">
@@ -995,7 +995,7 @@
       </c>
       <c r="C15" s="29">
         <f>COUNT(C3:C12)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F15" s="29">
         <f>COUNT(F3:F12)</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C16" s="30">
         <f>_xlfn.VAR.P(C3:C12)</f>
-        <v/>
+        <v>1.220116</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F16" s="30">
         <f>_xlfn.VAR.P(F3:F12)</f>
-        <v/>
+        <v>1.175289</v>
       </c>
     </row>
     <row r="18" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C19" s="31">
         <f>(C16*C15+F16*F15)/(C15+F15-2)</f>
-        <v/>
+        <v>1.33078055555556</v>
       </c>
     </row>
     <row r="20">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C20" s="32">
         <f>C14-F14</f>
-        <v/>
+        <v>0.863</v>
       </c>
     </row>
     <row r="21">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C21" s="33">
         <f>SQRT(C19*(1/C15+1/F15))</f>
-        <v/>
+        <v>0.515903199361189</v>
       </c>
     </row>
     <row r="22" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C22" s="34">
         <f>C20/C21</f>
-        <v/>
+        <v>1.67279443327469</v>
       </c>
     </row>
     <row r="23" ht="18.6" customHeight="1" s="24" thickBot="1">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C23" s="35">
         <f>_xlfn.T.INV.2T(0.05,C15+F15-2)</f>
-        <v/>
+        <v>2.10092204024104</v>
       </c>
     </row>
     <row r="24">
@@ -1095,9 +1095,9 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="35" t="str">
         <f>IF(ABS(C22)&gt;C23,"|t|&gt;確率95%のt → 差がある","|t|≦確率95%のt → 差があるとは言い切れない")</f>
-        <v/>
+        <v>|t|≦確率95%のt → 差があるとは言い切れない</v>
       </c>
     </row>
     <row r="26">
@@ -1113,9 +1113,9 @@
           <t>(1) F検定</t>
         </is>
       </c>
-      <c r="C27" s="36">
+      <c r="C27" s="36" t="str">
         <f>"F.TESTの値は"&amp;TEXT(H5,"0.0000")&amp;"で0.05"&amp;IF(H5&gt;0.05,"より大きいので、等分散と考えられる。","以下なので、不等分散と考えられる。")</f>
-        <v/>
+        <v>F.TESTの値は0.9564で0.05より大きいので、等分散と考えられる。</v>
       </c>
     </row>
     <row r="28">
@@ -1124,9 +1124,9 @@
           <t>(2) t検定(等分散)</t>
         </is>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="36" t="str">
         <f>"tの値は"&amp;TEXT(C22,"0.000")&amp;"、確率95%のtの値は"&amp;TEXT(C23,"0.000")&amp;"。tの値は確率95%の範囲("&amp;TEXT(-C23,"0.000")&amp;"～"&amp;TEXT(C23,"0.000")&amp;")の"&amp;IF(ABS(C22)&gt;C23,"外側にある。","内側にある。")</f>
-        <v/>
+        <v>tの値は1.673、確率95%のtの値は2.101。tの値は確率95%の範囲(-2.101～2.101)の内側にある。</v>
       </c>
     </row>
     <row r="29">
@@ -1135,9 +1135,9 @@
           <t>(3) tのP値</t>
         </is>
       </c>
-      <c r="C29" s="36">
+      <c r="C29" s="36" t="str">
         <f>"T.TESTで求めたP値は"&amp;TEXT(H8,"0.0000")&amp;"で0.05"&amp;IF(H8&lt;=0.05,"以下である。","より大きい。")</f>
-        <v/>
+        <v>T.TESTで求めたP値は0.1117で0.05より大きい。</v>
       </c>
     </row>
     <row r="30">
@@ -1146,9 +1146,9 @@
           <t>(4) 結論</t>
         </is>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="36" t="str">
         <f>IF(ABS(C22)&gt;C23,"帰無仮説は否定される。よって、自炊型とコンビニ型のキッチン面積には差があるといえる。","帰無仮説を否定できない。よって、自炊型とコンビニ型のキッチン面積に差があるとは言い切れない。")</f>
-        <v/>
+        <v>帰無仮説を否定できない。よって、自炊型とコンビニ型のキッチン面積に差があるとは言い切れない。</v>
       </c>
     </row>
   </sheetData>
